--- a/fundraiser_forms/008_orphanage_donation_form--fundraiser_forms.xlsx
+++ b/fundraiser_forms/008_orphanage_donation_form--fundraiser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,38 +520,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>orphanage_donation_form</t>
+          <t>donor_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>donation_amount</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Donor Name</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please enter your name</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>donor_info</t>
+          <t>donor_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>donor_info</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Donor Email</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter your email address</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -561,20 +569,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>donation_frequency</t>
+          <t>donor_amount</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>donation_frequency</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Donation Amount</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter the amount you wish to donate</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -584,22 +596,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>donor_address</t>
+          <t>donor_frequency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>donor_address</t>
+          <t>Donation Frequency</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Please provide your home address</t>
+          <t>Select your preferred frequency</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -611,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>donor_email</t>
+          <t>donor_method</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>donor_email</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Donation Method</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select your preferred donation method</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -639,111 +655,127 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>donor_phone</t>
+          <t>donor_address</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>donor_phone</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Donor Address</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide your home address</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>donation_notes</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>donation_notes</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Payment Method</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select your preferred payment method</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>donor_message</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Donor Message</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Share a message with us</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>donor_name</t>
+          <t>donor_other_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>donor_name</t>
+          <t>Other Frequency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Please enter your name</t>
+          <t>Select your preferred frequency</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>donor_message</t>
+          <t>donor_other_method</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>donor_message</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Other Method</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select your preferred donation method</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -758,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>donor_notes</t>
+          <t>orphanage_name</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>donor_notes</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Orphanage Name</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter the name of the orphanage</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -781,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>donor_other</t>
+          <t>orphanage_address</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Orphanage Address</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide the address of the orphanage</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -804,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>donor_other_notes</t>
+          <t>orphanage_email</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>other_notes</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Orphanage Email</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Enter the email address of the orphanage</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -827,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>donor_other_amount</t>
+          <t>orphanage_phone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>other_amount</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Orphanage Phone</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enter the phone number of the orphanage</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -845,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>donor_other_frequency</t>
+          <t>orphanage_notes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>other_frequency</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Orphanage Notes</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Add any notes about the orphanage</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -868,20 +920,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>donor_other_method</t>
+          <t>other_notes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>other_method</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Other Notes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Add any additional notes</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -896,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>orphanage_name</t>
+          <t>other_amount</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>orphanage_name</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Other Amount</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enter the amount of your donation</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -914,182 +974,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>orphanage_address</t>
+          <t>other_frequency</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>orphanage_address</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Other Frequency (2)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Select your preferred frequency</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>orphanage_email</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>orphanage_email</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>orphanage_phone</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>orphanage_phone</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>orphanage_notes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>orphanage_notes</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>orphanage_other</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>orphanage_other_notes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>other_notes</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>orphanage_other_amount</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>other_amount</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>orphanage_other_frequency</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>other_frequency</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1109,9 +1012,9 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1134,85 +1037,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>donor_info_choices</t>
+          <t>donor_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_doe'}</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Doe'}</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>donor_info_choices</t>
+          <t>donor_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>donation_frequency_choices</t>
+          <t>donor_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'one-time'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'One-time'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>donation_frequency_choices</t>
+          <t>donor_method_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'monthly'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Monthly'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>donation_frequency_choices</t>
+          <t>donor_method_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'quarterly'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Quarterly'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1127,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1144,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1161,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1178,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1195,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1309,46 +1212,46 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>orphanage_other_frequency_choices</t>
+          <t>other_frequency_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>orphanage_other_frequency_choices</t>
+          <t>other_frequency_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
